--- a/outputs/tables/tab4_robustness.xlsx
+++ b/outputs/tables/tab4_robustness.xlsx
@@ -54,28 +54,28 @@
     <t xml:space="preserve">Post2022 × Net exporter</t>
   </si>
   <si>
-    <t xml:space="preserve">1.790†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.975*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.332†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.920)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.789)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.902)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.768)</t>
+    <t xml:space="preserve">1.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.447)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.418)</t>
   </si>
   <si>
     <t xml:space="preserve">Country FE</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">253</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes. Sensitivity of β₃ (Post2022 × Net exporter) to excluding the countries with the most extreme subsidies. All columns use the TWFE specification of column (2) of Table 3; only the sample changes. Column (1) is the full sample (34 countries). Columns (2)–(4) exclude Venezuela (the net oil exporter with the highest subsidy, 18.1% of GDP), Suriname (the net oil importer with the highest subsidy, 8.5% of GDP), and both. Excluding each of the seven net oil exporters in turn gives estimates between 1.15 (without Venezuela) and 2.21 (without Guyana); this is a range of point estimates, not a confidence interval. Standard errors are clustered by country in parentheses. † p &lt; 0.10, * p &lt; 0.05, ** p &lt; 0.01, *** p &lt; 0.001. Source: IMF Fossil Fuel Subsidies Database.</t>
+    <t xml:space="preserve">Notes. Sensitivity of β₃ (Post2022 × Net exporter) to excluding the countries with the most extreme subsidies. All columns use the TWFE specification of column (2) of Table 3; only the sample changes. Column (1) is the full sample (34 countries). Columns (2)–(4) exclude Venezuela (the net oil exporter with the highest subsidy, 18.1% of GDP), Suriname (the net oil importer with the highest subsidy, 8.5% of GDP), and both. Excluding each of the five net oil exporters in turn gives estimates between 0.28 (without Venezuela) and 1.81 (without Brazil); this is a range of point estimates, not a confidence interval. Standard errors are clustered by country in parentheses. † p &lt; 0.10, * p &lt; 0.05, ** p &lt; 0.01, *** p &lt; 0.001. Source: IMF Fossil Fuel Subsidies Database.</t>
   </si>
 </sst>
 </file>
